--- a/labo/Y8960_Cartridge_TangPrimer25K_SSRAM_TEST/doc/Y8960_Cartridge_TangPrimer25K_pin.xlsx
+++ b/labo/Y8960_Cartridge_TangPrimer25K_SSRAM_TEST/doc/Y8960_Cartridge_TangPrimer25K_pin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\Y8960_Cartridge\fpga\Y8960_Cartridge_TangPrimer25K\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\labo\Y8960_Cartridge_TangPrimer25K_SSRAM_TEST\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A098AD-E377-4B5A-8D8A-9DD7E06EDC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F81300-B0CF-4F71-915E-8BDE41FD11D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TangPrimer25K" sheetId="2" r:id="rId1"/>
@@ -1193,7 +1193,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1258,12 +1258,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1910,7 +1904,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="22"/>
+      <c r="F5" s="1"/>
       <c r="G5" s="12"/>
       <c r="I5" s="8">
         <v>4</v>
@@ -2060,8 +2054,8 @@
         <v>2</v>
       </c>
       <c r="L7" s="1"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="23"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="12"/>
       <c r="P7" s="21">
         <v>67</v>
       </c>
@@ -2128,8 +2122,8 @@
         <v>2</v>
       </c>
       <c r="L8" s="1"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="23"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="12"/>
       <c r="P8" s="21">
         <v>69</v>
       </c>
@@ -2194,7 +2188,7 @@
         <v>2</v>
       </c>
       <c r="L9" s="1"/>
-      <c r="M9" s="22"/>
+      <c r="M9" s="1"/>
       <c r="N9" s="12"/>
       <c r="P9" s="21">
         <v>71</v>
@@ -2256,7 +2250,7 @@
         <v>2</v>
       </c>
       <c r="L10" s="1"/>
-      <c r="M10" s="22"/>
+      <c r="M10" s="1"/>
       <c r="N10" s="12"/>
       <c r="P10" s="21">
         <v>73</v>
@@ -2322,7 +2316,7 @@
         <v>2</v>
       </c>
       <c r="L11" s="1"/>
-      <c r="M11" s="22"/>
+      <c r="M11" s="1"/>
       <c r="N11" s="12"/>
       <c r="P11" s="8">
         <v>75</v>
@@ -3346,7 +3340,7 @@
         <v>106</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="Y26" s="1">
         <v>7</v>
@@ -3410,7 +3404,7 @@
         <v>108</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="Y27" s="1">
         <v>7</v>
